--- a/docs/산출물/19_한결공조_AS관리_소스이관목록_V1.1.xlsx
+++ b/docs/산출물/19_한결공조_AS관리_소스이관목록_V1.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\my-first-project\docs\산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D02F04A-0174-4161-A10E-DD22AE0B4D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A805A1-43DA-41F7-9C69-93B155CACB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="표지" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Flow" sheetId="9" r:id="rId9"/>
     <sheet name="Static Resource" sheetId="10" r:id="rId10"/>
     <sheet name="기타 메타데이터" sheetId="11" r:id="rId11"/>
+    <sheet name="배포 절차" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="484">
   <si>
     <t>문서번호</t>
   </si>
@@ -201,13 +202,6 @@
     <t>최초 작성</t>
   </si>
   <si>
-    <t>배포 절차서 V1.1 부록으로 최신화: 개발 샌드박스 → 운영 첫 배포 전제, 저장소에 모든 구성 요소 포함(retrieve 필요 항목 없음), 기사 배정·역할별 홈·누적 청구액·접수 자동 완료·승인 요청 요약·재고 공유 규칙 등 반영</t>
-  </si>
-  <si>
-    <t>※ 출처: 개발 샌드박스 조회 + 저장소 force-app(main 합침 기준) / 기준일 2026-10-16 / 반영대상 Y = 운영 이관 대상 / 배포 순서·명령은 배포 절차서 V1.1(docs/deploy_procedure.md)</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
     <t>테스트 클래스 29 포함</t>
   </si>
   <si>
@@ -1024,9 +1018,6 @@
     <t>CustomMetadata 레코드</t>
   </si>
   <si>
-    <t>ServiceSetting 11(출장비 50,000) · WarrantyPolicy 3 · ServiceCenterMapping 32 · TriggerSetting 4</t>
-  </si>
-  <si>
     <t>운영 기준값 확인(배포 절차서 5장)</t>
   </si>
   <si>
@@ -1132,9 +1123,6 @@
     <t>ListView · Report · Dashboard</t>
   </si>
   <si>
-    <t>목록 보기 32(배정 대기·재배정 필요·종결 대기·오늘 내가 받은 접수 등) · 리포트 4(폴더 2) · 대시보드 1</t>
-  </si>
-  <si>
     <t>목록 보기·리포트 폴더는 역할별 공유</t>
   </si>
   <si>
@@ -1166,6 +1154,373 @@
   </si>
   <si>
     <t>표준 오브젝트·필드 한국어 이름 9개</t>
+  </si>
+  <si>
+    <t>배포 절차 (개발 샌드박스 → 검증 샌드박스 → 운영 첫 배포)</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>※ 배포 절차서 V1.1(docs/deploy_procedure.md)의 순서를 한 장으로 요약 / 대상 = 이 목록의 반영대상 Y(manifest/package.xml) / 키·비밀값은 문서·Git에 쓰지 않고 설정 화면·비밀 저장소에만</t>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>단계</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업 · 명령</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>확인 기준</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>담당</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>시점</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>참조</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0. 사전 확인</t>
+  </si>
+  <si>
+    <t>샌드박스와 운영 차이 확인: 사용자 Username·승인자·ERP 주소·도로명주소 승인키·연동 OAuth 키, 데이터 없음</t>
+  </si>
+  <si>
+    <t>차이 목록 작성 완료</t>
+  </si>
+  <si>
+    <t>관리자</t>
+  </si>
+  <si>
+    <t>D-3</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>배포 직전 운영 백업: sf project retrieve start -o hg-prod --manifest manifest/package.xml --target-metadata-dir backup/hg-prod-&lt;날짜&gt; --unzip</t>
+  </si>
+  <si>
+    <t>백업 폴더 생성</t>
+  </si>
+  <si>
+    <t>D-1</t>
+  </si>
+  <si>
+    <t>8-1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1. 운영 org 준비</t>
+  </si>
+  <si>
+    <t>기능 활성화: Field Service 사용, 기본 사례 소유자, 관리자 Login As 허용 (경로·레이블 이름은 메타데이터로 배포)</t>
+  </si>
+  <si>
+    <t>설정 화면에서 켜짐 확인</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>라이선스: Salesforce + Field Service Standard(상담원·센터장·기사·관리자), Salesforce Integration + Salesforce API Integration(연동 사용자 1)</t>
+  </si>
+  <si>
+    <t>필요 수량 확보</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>재배포라면 예약 작업 해제: HG 반복 고장 재계산 · HG ERP 재전송 · HG ERP 재고 동기화 :30 (System.abortJob, 익명 Apex는 BOM 없는 UTF-8)</t>
+  </si>
+  <si>
+    <t>CronTrigger HG 0건</t>
+  </si>
+  <si>
+    <t>배포 직전</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>2. 환경별 값 수정</t>
+  </si>
+  <si>
+    <t>AP2 승인자 → 운영 센터장 Username / Named Credential HG_ErpMock → 운영 ERP 주소 / Case_AfterSave_UrgentAlert 실패 알림 관리자 / AP1 기준 금액 500000은 ApprovalAmount와 같게</t>
+  </si>
+  <si>
+    <t>4개 파일 수정 커밋</t>
+  </si>
+  <si>
+    <t>개발</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>3. 검증 배포</t>
+  </si>
+  <si>
+    <t>sf project deploy validate -o hg-prod --manifest manifest/package.xml --test-level RunLocalTests -w 120 (운영 변경 없음)</t>
+  </si>
+  <si>
+    <t>검증 성공 · 테스트 전부 통과 · 커버리지 75% 이상</t>
+  </si>
+  <si>
+    <t>D-day</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>실패 시: 예약 작업 참조(→5번), Unknown user permission(설정 먼저), 공유 규칙 체크박스 값 언어(참/True), 커버리지 부족, 단계 순서</t>
+  </si>
+  <si>
+    <t>원인 수정 후 다시 검증</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>4. 빠른 배포</t>
+  </si>
+  <si>
+    <t>sf project deploy quick -o hg-prod --job-id &lt;검증 Job Id&gt; -w 60 (검증 후 10일 안, 그 사이 운영 메타데이터 변경 금지)</t>
+  </si>
+  <si>
+    <t>배포 성공</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>단계로 나눌 때 순서: ① 기반(값 집합·오브젝트·필드·Custom Metadata·Custom Setting·라벨·사용자 지정 권한) ② 보안(역할·그룹·Queue·프로필·권한 집합·공유 규칙) ③ 코드(Apex·LWC·Aura) ④ 자동화(자격 증명·Flow·메일·승인·할당 규칙·빠른 작업) ⑤ 화면(레이아웃·FlexiPage·탭·앱·목록 보기·리포트·대시보드), 권한 집합은 코드·자동화 뒤 다시</t>
+  </si>
+  <si>
+    <t>단계별 성공</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>5. 배포 후 수동 설정</t>
+  </si>
+  <si>
+    <t>비밀값 입력: 도로명주소 승인키(HG_JusoPrincipal ConfmKey) · ERP API 키(HG_ErpPrincipal ApiKey) · 외부 클라이언트 앱 HG ERP Mock 소비자 키·비밀 발급 → ERP 비밀 저장소</t>
+  </si>
+  <si>
+    <t>주소 검색·ERP 호출·푸시 성공</t>
+  </si>
+  <si>
+    <t>5 (1~3)</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>사용자 생성 · 프로필(HG 콜센터 상담원·HG 센터장·HG 협력 기사) · 역할 · 기사 Manager = 소속 센터장 · 권한 집합(HG_CallCenter·HG_CenterManager·HG_Technician·HG_Admin) + Field Service Standard 할당 · 연동 사용자(HG_ErpIntegration·HG_ErpIntegrationData)</t>
+  </si>
+  <si>
+    <t>사용자별 할당 확인</t>
+  </si>
+  <si>
+    <t>2-3 · 2-4 · 5 (4)</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>프로필별 레이아웃(고객사 레코드 유형 4 · 제품 레이아웃 — 없으면 제품 화면 오류) · 앱 홈 지정 · 리포트·대시보드 탭(기사 숨김) · 할당 규칙 HG_CaseByServiceCenter 활성</t>
+  </si>
+  <si>
+    <t>역할별 화면 열림</t>
+  </si>
+  <si>
+    <t>5 (5~7)</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>예약 작업 등록: d6_schedule.apex · d7_erp_retry_schedule.apex · d7_erp_inbound_schedule.apex(APPLY = true) / ERP 기준 이력 번호 d7_erp_inbound_baseline.apex(1회)</t>
+  </si>
+  <si>
+    <t>CronTrigger 3건 WAITING</t>
+  </si>
+  <si>
+    <t>5 (8~9)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>운영 기준값 확인: 승인 기준 500,000 · 출장비 50,000 · 반복 고장 90일 3회 · SLA 24/48 · ERP 재시도 3 · 보증 12/36/24개월 · TriggerSetting 5 활성</t>
+  </si>
+  <si>
+    <t>값 확인</t>
+  </si>
+  <si>
+    <t>5 (10)</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>6. 데이터 이관</t>
+  </si>
+  <si>
+    <t>부모 → 자식 순서 upsert: 제품(ErpPartCode__c, ERP 단가) → 가격표 항목 → 고객사(사업자번호) → 사업장(SiteCode__c, 행정구역 코드) → 장비(SerialKey__c) → 위치·재고(차량 재고 소유자 = 기사)</t>
+  </si>
+  <si>
+    <t>오브젝트별 원본 건수 = 적재 건수, 외부 ID 중복 0</t>
+  </si>
+  <si>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>대량 적재 시 TriggerSetting으로 해당 트리거 잠시 끔 → 적재 후 켜고 집계 스크립트(d6_backfill · d9_asset_charge_backfill · d9_parent_charge_backfill) / 과거 사용 부품은 ERP 상태를 비워 넣음(이중 차감 방지)</t>
+  </si>
+  <si>
+    <t>장비 고객사·사업장 서비스센터·출동 서비스센터 누락 0</t>
+  </si>
+  <si>
+    <t>6-1 · 6-3</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>ERP 재고 맞추기: Salesforce 재고 = ERP 재고(위치·부품별), 처음이면 d7_erp_seed.apex(대기·실패 건 있으면 중단)</t>
+  </si>
+  <si>
+    <t>재고 불일치 0</t>
+  </si>
+  <si>
+    <t>6-4</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>7. 배포 직후 점검</t>
+  </si>
+  <si>
+    <t>역할별 로그인·홈 / 상담원 가상 착신 → 접수 저장(소유자 = 센터 Queue) / 센터장 [기사 배정] / 기사 수락·도착·부품 추가(초과 거부·ERP 완료) / [승인 요청] → 센터장 승인 / 출동 완료 → 접수 자동 완료 → 종결 / 다른 센터 데이터 안 보임 / 예약 작업 3건 · ERP 입고 푸시</t>
+  </si>
+  <si>
+    <t>8개 항목 모두 기대 결과</t>
+  </si>
+  <si>
+    <t>관리자 · 사용자 대표</t>
+  </si>
+  <si>
+    <t>D-day 30분</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>8. 롤백</t>
+  </si>
+  <si>
+    <t>검증 실패 → 운영 변경 없음 / 빠른 배포 후 문제 → 2번 백업 또는 이전 릴리스 커밋으로 검증 → 빠른 배포, 새 구성 요소는 destructiveChanges.xml / 트리거 문제 → TriggerSetting IsActive false로 즉시 중지 / ERP 문제 → 예약 해제·외부 클라이언트 앱 비활성</t>
+  </si>
+  <si>
+    <t>판단: 7번 점검 1건이라도 실패하면 오픈 보류</t>
+  </si>
+  <si>
+    <t>필요 시</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>되돌릴 수 없는 것: 배포 후 입력 데이터 · 이미 ERP로 보낸 차감(ERP 조정 → 역방향 반영) · 삭제 배포한 필드(삭제 전 export) · 보낸 메일</t>
+  </si>
+  <si>
+    <t>대응 방법 공유</t>
+  </si>
+  <si>
+    <t>8-2</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>9. 확인</t>
+  </si>
+  <si>
+    <t>배포 후 차이 확인: sf project retrieve start -o hg-prod --manifest manifest/package.xml --target-metadata-dir retrieve_check --unzip → 저장소와 비교(순서·포맷 외 차이는 원인 기록)</t>
+  </si>
+  <si>
+    <t>내용 차이 0</t>
+  </si>
+  <si>
+    <t>D+1</t>
+  </si>
+  <si>
+    <t>4-4</t>
+  </si>
+  <si>
+    <t>배포 절차서 V1.1 부록으로 최신화: 개발 샌드박스 → 운영 첫 배포 전제, 저장소에 모든 구성 요소 포함(retrieve 필요 항목 없음), 기사 배정·역할별 홈·누적 청구액·접수 자동 완료·승인 요청 요약·재고 공유 규칙 등 반영 / 2026-10-19 배포 절차 시트 추가(배포 절차서 V1.1 1~8장 요약)</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>※ 출처: 개발 샌드박스 조회 + 저장소 force-app(main 합침 기준) / 기준일 2026-10-16 / 반영대상 Y = 운영 이관 대상 / 배포 순서·명령은 [배포 절차] 시트와 배포 절차서 V1.1(docs/deploy_procedure.md)</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>ServiceSetting 11(출장비 50,000) · WarrantyPolicy 3 · ServiceCenterMapping 32 · TriggerSetting 5(사업장 CustomerSite 추가 2026-10-18)</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.10.18</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>목록 보기 33(배정 대기·재배정 필요 접수·종결 대기·오늘 내가 받은 접수 등) · 리포트 4(폴더 2) · 대시보드 1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1317,7 +1672,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1344,16 +1699,29 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1365,13 +1733,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1867,105 +2231,105 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5">
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="11"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="13"/>
+      <c r="E13" s="17"/>
     </row>
     <row r="14" spans="2:5">
       <c r="C14" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="13"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="16">
         <v>46311</v>
       </c>
-      <c r="E15" s="13"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" spans="2:5">
       <c r="C16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="13"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="13"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" spans="3:5">
       <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="3:5">
       <c r="C19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="13"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2038,22 +2402,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="24">
@@ -2061,22 +2425,22 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="24">
@@ -2084,22 +2448,22 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="24">
@@ -2107,22 +2471,22 @@
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="24">
@@ -2130,22 +2494,22 @@
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="24">
@@ -2153,22 +2517,22 @@
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="24">
@@ -2176,22 +2540,22 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="24">
@@ -2199,22 +2563,22 @@
         <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="24">
@@ -2222,22 +2586,22 @@
         <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="24">
@@ -2245,22 +2609,22 @@
         <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="24">
@@ -2268,22 +2632,22 @@
         <v>11</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="24">
@@ -2291,22 +2655,22 @@
         <v>12</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="24">
@@ -2314,22 +2678,22 @@
         <v>13</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="24">
@@ -2337,22 +2701,22 @@
         <v>14</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="24">
@@ -2360,22 +2724,22 @@
         <v>15</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="24">
@@ -2383,22 +2747,22 @@
         <v>16</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="24">
@@ -2406,22 +2770,22 @@
         <v>17</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="24">
@@ -2429,22 +2793,22 @@
         <v>18</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="24">
@@ -2452,22 +2816,22 @@
         <v>19</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="24">
@@ -2475,22 +2839,22 @@
         <v>20</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="24">
@@ -2498,22 +2862,22 @@
         <v>21</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="24">
@@ -2521,22 +2885,22 @@
         <v>22</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="24">
@@ -2544,22 +2908,22 @@
         <v>23</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="24">
@@ -2567,22 +2931,22 @@
         <v>24</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="24">
@@ -2590,22 +2954,22 @@
         <v>25</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="24">
@@ -2613,22 +2977,22 @@
         <v>26</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="24">
@@ -2636,22 +3000,22 @@
         <v>27</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="24">
@@ -2659,22 +3023,22 @@
         <v>28</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="24">
@@ -2682,22 +3046,22 @@
         <v>29</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="24">
@@ -2705,22 +3069,22 @@
         <v>30</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="24">
@@ -2728,22 +3092,22 @@
         <v>31</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="24">
@@ -2751,22 +3115,22 @@
         <v>32</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -2794,7 +3158,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="20.25">
       <c r="B2" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -2802,10 +3166,10 @@
         <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>29</v>
@@ -2825,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>33</v>
@@ -2837,21 +3201,21 @@
         <v>46</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="36">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="48">
       <c r="B6" s="7">
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>322</v>
+        <v>481</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>33</v>
@@ -2859,11 +3223,11 @@
       <c r="F6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>108</v>
+      <c r="G6" s="24" t="s">
+        <v>482</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="2:8">
@@ -2871,10 +3235,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>33</v>
@@ -2883,10 +3247,10 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="24">
@@ -2894,10 +3258,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>33</v>
@@ -2906,7 +3270,7 @@
         <v>46</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H8" s="6"/>
     </row>
@@ -2915,10 +3279,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>33</v>
@@ -2927,7 +3291,7 @@
         <v>46</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H9" s="6"/>
     </row>
@@ -2936,10 +3300,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>33</v>
@@ -2948,10 +3312,10 @@
         <v>46</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="24">
@@ -2959,10 +3323,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>33</v>
@@ -2971,7 +3335,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H11" s="6"/>
     </row>
@@ -2980,10 +3344,10 @@
         <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>33</v>
@@ -2992,10 +3356,10 @@
         <v>46</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="60">
@@ -3003,10 +3367,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>33</v>
@@ -3015,10 +3379,10 @@
         <v>46</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="24">
@@ -3026,10 +3390,10 @@
         <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>33</v>
@@ -3038,10 +3402,10 @@
         <v>46</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="36">
@@ -3049,10 +3413,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>33</v>
@@ -3061,10 +3425,10 @@
         <v>46</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="2:8">
@@ -3072,10 +3436,10 @@
         <v>12</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>33</v>
@@ -3084,7 +3448,7 @@
         <v>46</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H16" s="6"/>
     </row>
@@ -3093,10 +3457,10 @@
         <v>13</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>33</v>
@@ -3105,10 +3469,10 @@
         <v>46</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="48">
@@ -3116,10 +3480,10 @@
         <v>14</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>33</v>
@@ -3128,7 +3492,7 @@
         <v>46</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H18" s="6"/>
     </row>
@@ -3137,10 +3501,10 @@
         <v>15</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>33</v>
@@ -3149,7 +3513,7 @@
         <v>46</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H19" s="6"/>
     </row>
@@ -3158,10 +3522,10 @@
         <v>16</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>358</v>
+        <v>483</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>33</v>
@@ -3169,11 +3533,11 @@
       <c r="F20" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>108</v>
+      <c r="G20" s="24" t="s">
+        <v>482</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="24">
@@ -3181,10 +3545,10 @@
         <v>17</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>33</v>
@@ -3193,7 +3557,7 @@
         <v>46</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H21" s="6"/>
     </row>
@@ -3202,10 +3566,10 @@
         <v>18</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>33</v>
@@ -3214,10 +3578,10 @@
         <v>46</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="24">
@@ -3225,10 +3589,10 @@
         <v>19</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>33</v>
@@ -3237,10 +3601,10 @@
         <v>46</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="24" spans="2:8">
@@ -3248,10 +3612,10 @@
         <v>20</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>33</v>
@@ -3260,9 +3624,572 @@
         <v>46</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H24" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9572302-65B6-4583-879F-7DB80ACDC674}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:H26"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="5" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="4" max="4" width="70.625" customWidth="1"/>
+    <col min="5" max="5" width="30.625" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="11.625" customWidth="1"/>
+    <col min="8" max="8" width="14.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="20.25">
+      <c r="B2" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="B3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="24">
+      <c r="B5" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="24">
+      <c r="B6" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="24">
+      <c r="B7" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="24">
+      <c r="B8" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="24">
+      <c r="B9" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="24">
+      <c r="B10" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="24">
+      <c r="B11" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="24">
+      <c r="B12" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="24">
+      <c r="B13" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="48">
+      <c r="B14" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="24">
+      <c r="B15" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="36">
+      <c r="B16" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="24">
+      <c r="B17" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="24">
+      <c r="B18" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="24">
+      <c r="B19" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="24">
+      <c r="B20" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="36">
+      <c r="B21" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="24">
+      <c r="B22" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="36">
+      <c r="B23" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="36">
+      <c r="B24" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="24">
+      <c r="B25" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="24">
+      <c r="B26" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>478</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
@@ -3308,7 +4235,7 @@
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="10">
         <v>46311</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -3322,14 +4249,14 @@
       <c r="B6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="11">
         <v>46311</v>
       </c>
       <c r="D6" t="s">
         <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -3358,12 +4285,12 @@
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="B3" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
     </row>
     <row r="5" spans="2:5" ht="27.95" customHeight="1">
       <c r="B5" s="5" t="s">
@@ -3390,7 +4317,7 @@
         <v>62</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="2:5">
@@ -3404,7 +4331,7 @@
         <v>5</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -3418,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -3444,7 +4371,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -3470,12 +4397,12 @@
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C13" s="7">
         <v>20</v>
@@ -3484,7 +4411,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="2:5">
@@ -3566,7 +4493,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D5" s="6">
         <v>67</v>
@@ -3575,19 +4502,19 @@
         <v>32</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="36">
@@ -3595,28 +4522,28 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="6">
+        <v>67</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="6">
-        <v>67</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="J6" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="48">
@@ -3624,28 +4551,28 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="6">
+        <v>67</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="6">
-        <v>67</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="J7" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="36">
@@ -3653,7 +4580,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D8" s="6">
         <v>67</v>
@@ -3662,19 +4589,19 @@
         <v>32</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="48">
@@ -3682,28 +4609,28 @@
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="6">
+        <v>67</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="D9" s="6">
-        <v>67</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="24">
@@ -3711,28 +4638,28 @@
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="6">
+        <v>67</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="D10" s="6">
-        <v>67</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="24">
@@ -3740,7 +4667,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D11" s="6">
         <v>67</v>
@@ -3749,19 +4676,19 @@
         <v>32</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="24">
@@ -3769,28 +4696,28 @@
         <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="6">
+        <v>67</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="6">
-        <v>67</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="J12" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="36">
@@ -3798,7 +4725,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D13" s="6">
         <v>67</v>
@@ -3807,19 +4734,19 @@
         <v>32</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I13" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="48">
@@ -3827,28 +4754,28 @@
         <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="6">
+        <v>67</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="D14" s="6">
-        <v>67</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="36">
@@ -3856,28 +4783,28 @@
         <v>11</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="6">
+        <v>67</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="D15" s="6">
-        <v>67</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="24">
@@ -3885,28 +4812,28 @@
         <v>12</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="6">
+        <v>67</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="6">
-        <v>67</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="J16" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="24">
@@ -3914,7 +4841,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D17" s="6">
         <v>67</v>
@@ -3923,19 +4850,19 @@
         <v>32</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="24">
@@ -3943,28 +4870,28 @@
         <v>14</v>
       </c>
       <c r="C18" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="6">
+        <v>67</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="D18" s="6">
-        <v>67</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="36">
@@ -3972,28 +4899,28 @@
         <v>15</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="6">
+        <v>67</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="D19" s="6">
-        <v>67</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="36">
@@ -4001,28 +4928,28 @@
         <v>16</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="6">
+        <v>67</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="D20" s="6">
-        <v>67</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="21" spans="2:10">
@@ -4030,28 +4957,28 @@
         <v>17</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="6">
+        <v>67</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="D21" s="6">
-        <v>67</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="36">
@@ -4059,28 +4986,28 @@
         <v>18</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="6">
+        <v>67</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="D22" s="6">
-        <v>67</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="23" spans="2:10">
@@ -4088,28 +5015,28 @@
         <v>19</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="6">
+        <v>67</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="6">
-        <v>67</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="6" t="s">
+      <c r="J23" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="24" spans="2:10" ht="36">
@@ -4117,7 +5044,7 @@
         <v>20</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D24" s="6">
         <v>67</v>
@@ -4126,19 +5053,19 @@
         <v>32</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="24">
@@ -4146,28 +5073,28 @@
         <v>21</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="6">
+        <v>67</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="6">
-        <v>67</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="6" t="s">
+      <c r="J25" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="26" spans="2:10" ht="60">
@@ -4175,7 +5102,7 @@
         <v>22</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D26" s="6">
         <v>67</v>
@@ -4184,19 +5111,19 @@
         <v>32</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I26" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="24">
@@ -4204,28 +5131,28 @@
         <v>23</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="6">
+        <v>67</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="D27" s="6">
-        <v>67</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="36">
@@ -4233,28 +5160,28 @@
         <v>24</v>
       </c>
       <c r="C28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="6">
+        <v>67</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J28" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="D28" s="6">
-        <v>67</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="29" spans="2:10" ht="36">
@@ -4262,28 +5189,28 @@
         <v>25</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="6">
+        <v>67</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J29" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="D29" s="6">
-        <v>67</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="30" spans="2:10" ht="36">
@@ -4291,28 +5218,28 @@
         <v>26</v>
       </c>
       <c r="C30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" s="6">
+        <v>67</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J30" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="D30" s="6">
-        <v>67</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="31" spans="2:10" ht="36">
@@ -4320,28 +5247,28 @@
         <v>27</v>
       </c>
       <c r="C31" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="6">
+        <v>67</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J31" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="D31" s="6">
-        <v>67</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="32" spans="2:10" ht="24">
@@ -4349,28 +5276,28 @@
         <v>28</v>
       </c>
       <c r="C32" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="6">
+        <v>67</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J32" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D32" s="6">
-        <v>67</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="36">
@@ -4378,28 +5305,28 @@
         <v>29</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="6">
+        <v>67</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J33" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="D33" s="6">
-        <v>67</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="34" spans="2:10" ht="48">
@@ -4407,28 +5334,28 @@
         <v>30</v>
       </c>
       <c r="C34" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="6">
+        <v>67</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J34" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="D34" s="6">
-        <v>67</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="35" spans="2:10" ht="36">
@@ -4436,28 +5363,28 @@
         <v>31</v>
       </c>
       <c r="C35" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" s="6">
+        <v>67</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J35" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="D35" s="6">
-        <v>67</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="36" spans="2:10" ht="24">
@@ -4465,28 +5392,28 @@
         <v>32</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="6">
+        <v>67</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J36" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="D36" s="6">
-        <v>67</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="48">
@@ -4494,28 +5421,28 @@
         <v>33</v>
       </c>
       <c r="C37" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" s="6">
+        <v>67</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J37" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="D37" s="6">
-        <v>67</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="38" spans="2:10" ht="60">
@@ -4523,28 +5450,28 @@
         <v>34</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="6">
+        <v>67</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J38" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="D38" s="6">
-        <v>67</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="39" spans="2:10" ht="48">
@@ -4552,7 +5479,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D39" s="6">
         <v>67</v>
@@ -4561,19 +5488,19 @@
         <v>32</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="2:10" ht="24">
@@ -4581,7 +5508,7 @@
         <v>36</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D40" s="6">
         <v>67</v>
@@ -4590,19 +5517,19 @@
         <v>32</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="2:10" ht="60">
@@ -4610,7 +5537,7 @@
         <v>37</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D41" s="6">
         <v>67</v>
@@ -4619,19 +5546,19 @@
         <v>32</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="2:10" ht="24">
@@ -4639,28 +5566,28 @@
         <v>38</v>
       </c>
       <c r="C42" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42" s="6">
+        <v>67</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J42" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="D42" s="6">
-        <v>67</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="43" spans="2:10" ht="48">
@@ -4668,28 +5595,28 @@
         <v>39</v>
       </c>
       <c r="C43" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" s="6">
+        <v>67</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J43" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="D43" s="6">
-        <v>67</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="44" spans="2:10" ht="36">
@@ -4697,7 +5624,7 @@
         <v>40</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D44" s="6">
         <v>67</v>
@@ -4706,19 +5633,19 @@
         <v>32</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="2:10" ht="48">
@@ -4726,28 +5653,28 @@
         <v>41</v>
       </c>
       <c r="C45" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" s="6">
+        <v>67</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J45" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="D45" s="6">
-        <v>67</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="46" spans="2:10" ht="48">
@@ -4755,28 +5682,28 @@
         <v>42</v>
       </c>
       <c r="C46" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D46" s="6">
+        <v>67</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J46" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="D46" s="6">
-        <v>67</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="47" spans="2:10" ht="24">
@@ -4784,7 +5711,7 @@
         <v>43</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D47" s="6">
         <v>67</v>
@@ -4793,19 +5720,19 @@
         <v>32</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="2:10" ht="36">
@@ -4813,7 +5740,7 @@
         <v>44</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D48" s="6">
         <v>67</v>
@@ -4822,19 +5749,19 @@
         <v>32</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="2:10" ht="36">
@@ -4842,28 +5769,28 @@
         <v>45</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49" s="6">
+        <v>67</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J49" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="D49" s="6">
-        <v>67</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="50" spans="2:10" ht="36">
@@ -4871,28 +5798,28 @@
         <v>46</v>
       </c>
       <c r="C50" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D50" s="6">
+        <v>67</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J50" s="6" t="s">
         <v>156</v>
-      </c>
-      <c r="D50" s="6">
-        <v>67</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="51" spans="2:10" ht="24">
@@ -4900,28 +5827,28 @@
         <v>47</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D51" s="6">
+        <v>67</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J51" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="D51" s="6">
-        <v>67</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="52" spans="2:10" ht="48">
@@ -4929,28 +5856,28 @@
         <v>48</v>
       </c>
       <c r="C52" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D52" s="6">
+        <v>67</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J52" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="D52" s="6">
-        <v>67</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="53" spans="2:10" ht="48">
@@ -4958,28 +5885,28 @@
         <v>49</v>
       </c>
       <c r="C53" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D53" s="6">
+        <v>67</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J53" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="D53" s="6">
-        <v>67</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J53" s="6" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="54" spans="2:10" ht="24">
@@ -4987,28 +5914,28 @@
         <v>50</v>
       </c>
       <c r="C54" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D54" s="6">
+        <v>67</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J54" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="D54" s="6">
-        <v>67</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="55" spans="2:10" ht="24">
@@ -5016,28 +5943,28 @@
         <v>51</v>
       </c>
       <c r="C55" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D55" s="6">
+        <v>67</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J55" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="D55" s="6">
-        <v>67</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J55" s="6" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="56" spans="2:10" ht="36">
@@ -5045,28 +5972,28 @@
         <v>52</v>
       </c>
       <c r="C56" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" s="6">
+        <v>67</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J56" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="D56" s="6">
-        <v>67</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="57" spans="2:10" ht="36">
@@ -5074,28 +6001,28 @@
         <v>53</v>
       </c>
       <c r="C57" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D57" s="6">
+        <v>67</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J57" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="D57" s="6">
-        <v>67</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="58" spans="2:10" ht="36">
@@ -5103,28 +6030,28 @@
         <v>54</v>
       </c>
       <c r="C58" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D58" s="6">
+        <v>67</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J58" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="D58" s="6">
-        <v>67</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J58" s="6" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="59" spans="2:10" ht="36">
@@ -5132,28 +6059,28 @@
         <v>55</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D59" s="6">
+        <v>67</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J59" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="D59" s="6">
-        <v>67</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J59" s="6" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="60" spans="2:10" ht="48">
@@ -5161,7 +6088,7 @@
         <v>56</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D60" s="6">
         <v>67</v>
@@ -5170,19 +6097,19 @@
         <v>32</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="2:10" ht="72">
@@ -5190,7 +6117,7 @@
         <v>57</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D61" s="6">
         <v>67</v>
@@ -5199,19 +6126,19 @@
         <v>32</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" spans="2:10" ht="60">
@@ -5219,28 +6146,28 @@
         <v>58</v>
       </c>
       <c r="C62" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D62" s="6">
+        <v>67</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J62" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="D62" s="6">
-        <v>67</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="G62" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="J62" s="6" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="63" spans="2:10" ht="60">
@@ -5248,28 +6175,28 @@
         <v>59</v>
       </c>
       <c r="C63" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D63" s="6">
+        <v>67</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J63" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="D63" s="6">
-        <v>67</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="J63" s="6" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="64" spans="2:10" ht="36">
@@ -5277,28 +6204,28 @@
         <v>60</v>
       </c>
       <c r="C64" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D64" s="6">
+        <v>67</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J64" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="D64" s="6">
-        <v>67</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J64" s="6" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="65" spans="2:10" ht="48">
@@ -5306,28 +6233,28 @@
         <v>61</v>
       </c>
       <c r="C65" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D65" s="6">
+        <v>67</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J65" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="D65" s="6">
-        <v>67</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J65" s="6" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="66" spans="2:10">
@@ -5335,7 +6262,7 @@
         <v>62</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D66" s="6">
         <v>67</v>
@@ -5344,19 +6271,19 @@
         <v>32</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -5423,7 +6350,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D5" s="6">
         <v>67</v>
@@ -5432,19 +6359,19 @@
         <v>32</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="24">
@@ -5452,28 +6379,28 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="6">
+        <v>67</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="D6" s="6">
-        <v>67</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="36">
@@ -5481,28 +6408,28 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="6">
+        <v>67</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="D7" s="6">
-        <v>67</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="24">
@@ -5510,7 +6437,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D8" s="6">
         <v>67</v>
@@ -5519,19 +6446,19 @@
         <v>32</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="24">
@@ -5539,28 +6466,28 @@
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="6">
+        <v>67</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="D9" s="6">
-        <v>67</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -5624,10 +6551,10 @@
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -5705,16 +6632,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E5" s="6" t="b">
         <v>1</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G5" s="6">
         <v>67</v>
@@ -5723,10 +6650,10 @@
         <v>33</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K5" s="6"/>
     </row>
@@ -5735,16 +6662,16 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E6" s="6" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G6" s="6">
         <v>67</v>
@@ -5753,10 +6680,10 @@
         <v>33</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K6" s="6"/>
     </row>
@@ -5765,16 +6692,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E7" s="6" t="b">
         <v>0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G7" s="6">
         <v>67</v>
@@ -5783,10 +6710,10 @@
         <v>33</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K7" s="6"/>
     </row>
@@ -5795,16 +6722,16 @@
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E8" s="6" t="b">
         <v>1</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G8" s="6">
         <v>67</v>
@@ -5813,10 +6740,10 @@
         <v>33</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K8" s="6"/>
     </row>
@@ -5825,16 +6752,16 @@
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E9" s="6" t="b">
         <v>0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G9" s="6">
         <v>67</v>
@@ -5843,10 +6770,10 @@
         <v>33</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K9" s="6"/>
     </row>
@@ -5855,16 +6782,16 @@
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E10" s="6" t="b">
         <v>1</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G10" s="6">
         <v>67</v>
@@ -5873,10 +6800,10 @@
         <v>33</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K10" s="6"/>
     </row>
@@ -5885,16 +6812,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E11" s="6" t="b">
         <v>0</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G11" s="6">
         <v>67</v>
@@ -5903,10 +6830,10 @@
         <v>33</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K11" s="6"/>
     </row>
@@ -5915,16 +6842,16 @@
         <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E12" s="6" t="b">
         <v>0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G12" s="6">
         <v>67</v>
@@ -5933,10 +6860,10 @@
         <v>33</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K12" s="6"/>
     </row>
@@ -5945,16 +6872,16 @@
         <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E13" s="6" t="b">
         <v>1</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G13" s="6">
         <v>67</v>
@@ -5963,10 +6890,10 @@
         <v>33</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K13" s="6"/>
     </row>
@@ -5975,16 +6902,16 @@
         <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E14" s="6" t="b">
         <v>0</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G14" s="6">
         <v>67</v>
@@ -5993,10 +6920,10 @@
         <v>33</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K14" s="6"/>
     </row>
@@ -6005,16 +6932,16 @@
         <v>11</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E15" s="6" t="b">
         <v>1</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G15" s="6">
         <v>67</v>
@@ -6023,10 +6950,10 @@
         <v>33</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K15" s="6"/>
     </row>
@@ -6035,16 +6962,16 @@
         <v>12</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E16" s="6" t="b">
         <v>0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G16" s="6">
         <v>67</v>
@@ -6053,10 +6980,10 @@
         <v>33</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K16" s="6"/>
     </row>
@@ -6065,10 +6992,10 @@
         <v>13</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E17" s="6" t="b">
         <v>0</v>
@@ -6081,10 +7008,10 @@
         <v>33</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K17" s="6"/>
     </row>
@@ -6093,16 +7020,16 @@
         <v>14</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E18" s="6" t="b">
         <v>0</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G18" s="6">
         <v>67</v>
@@ -6111,10 +7038,10 @@
         <v>33</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K18" s="6"/>
     </row>
@@ -6123,16 +7050,16 @@
         <v>15</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E19" s="6" t="b">
         <v>1</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G19" s="6">
         <v>67</v>
@@ -6141,10 +7068,10 @@
         <v>33</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K19" s="6"/>
     </row>
@@ -6153,16 +7080,16 @@
         <v>16</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E20" s="6" t="b">
         <v>1</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G20" s="6">
         <v>67</v>
@@ -6171,10 +7098,10 @@
         <v>33</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K20" s="6"/>
     </row>
@@ -6242,13 +7169,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F5" s="6">
         <v>67</v>
@@ -6257,10 +7184,10 @@
         <v>33</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -6269,13 +7196,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F6" s="6">
         <v>67</v>
@@ -6284,10 +7211,10 @@
         <v>33</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J6" s="6"/>
     </row>
@@ -6355,7 +7282,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>39</v>
@@ -6364,16 +7291,16 @@
         <v>32</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -6382,7 +7309,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>39</v>
@@ -6391,16 +7318,16 @@
         <v>32</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J6" s="6"/>
     </row>
@@ -6409,7 +7336,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>39</v>
@@ -6418,16 +7345,16 @@
         <v>32</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J7" s="6"/>
     </row>
@@ -6436,7 +7363,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>39</v>
@@ -6445,16 +7372,16 @@
         <v>32</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J8" s="6"/>
     </row>
@@ -6463,7 +7390,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>21</v>
@@ -6472,16 +7399,16 @@
         <v>32</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J9" s="6"/>
     </row>
@@ -6490,7 +7417,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>21</v>
@@ -6499,16 +7426,16 @@
         <v>32</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J10" s="6"/>
     </row>
@@ -6517,7 +7444,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>39</v>
@@ -6526,16 +7453,16 @@
         <v>32</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J11" s="6"/>
     </row>
@@ -6544,7 +7471,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>39</v>
@@ -6553,16 +7480,16 @@
         <v>32</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J12" s="6"/>
     </row>
@@ -6571,7 +7498,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>39</v>
@@ -6580,16 +7507,16 @@
         <v>32</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J13" s="6"/>
     </row>
@@ -6598,7 +7525,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>39</v>
@@ -6607,16 +7534,16 @@
         <v>32</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J14" s="6"/>
     </row>
@@ -6625,7 +7552,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>39</v>
@@ -6634,16 +7561,16 @@
         <v>32</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J15" s="6"/>
     </row>
@@ -6652,7 +7579,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>39</v>
@@ -6661,16 +7588,16 @@
         <v>32</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J16" s="6"/>
     </row>
@@ -6679,7 +7606,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>21</v>
@@ -6688,16 +7615,16 @@
         <v>32</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -6706,7 +7633,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>39</v>
@@ -6715,16 +7642,16 @@
         <v>32</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J18" s="6"/>
     </row>
@@ -6736,14 +7663,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x01010065F9ABE2E9073F4DBEFD3A0E4E804736" ma:contentTypeVersion="15" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="e21f2c0381dcdb676ff4d058d9391828">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="355e9163-e205-4f55-8724-e062aa2d762e" xmlns:ns3="b82e25f1-f1d4-4b57-be84-1f5ad188becc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74ede542eddc1547cf48ce9271227341" ns2:_="" ns3:_="">
     <xsd:import namespace="355e9163-e205-4f55-8724-e062aa2d762e"/>
@@ -6978,7 +7897,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="b82e25f1-f1d4-4b57-be84-1f5ad188becc" xsi:nil="true"/>
@@ -6989,15 +7908,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E28766F-3A85-4DB5-A34A-161B525EA00C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7755F2D-D2B6-4964-8521-44D80E3F4BD4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7016,7 +7935,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C50EDEB0-E44B-4671-9975-DE1AF8797966}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7025,4 +7944,12 @@
     <ds:schemaRef ds:uri="355e9163-e205-4f55-8724-e062aa2d762e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E28766F-3A85-4DB5-A34A-161B525EA00C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>